--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81458</v>
+        <v>81462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90844</v>
+        <v>90846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91467</v>
+        <v>91469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92504</v>
+        <v>92506</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81462</v>
+        <v>81464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91469</v>
+        <v>91471</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92506</v>
+        <v>92508</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81464</v>
+        <v>81465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91471</v>
+        <v>91472</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92508</v>
+        <v>92509</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93436</v>
+        <v>93437</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93436</v>
+        <v>93437</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93436</v>
+        <v>93437</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93436</v>
+        <v>93437</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90849</v>
+        <v>90855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92509</v>
+        <v>92515</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93437</v>
+        <v>93443</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93437</v>
+        <v>93443</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93437</v>
+        <v>93443</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93437</v>
+        <v>93443</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81465</v>
+        <v>81467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90855</v>
+        <v>90859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91478</v>
+        <v>91482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92515</v>
+        <v>92519</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93443</v>
+        <v>93447</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93443</v>
+        <v>93447</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93443</v>
+        <v>93447</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93443</v>
+        <v>93447</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -10221,7 +10221,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81467</v>
+        <v>81457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92519</v>
+        <v>92521</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81457</v>
+        <v>81470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90861</v>
+        <v>90874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91484</v>
+        <v>91497</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>137017516</v>
       </c>
       <c r="B56" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>137017522</v>
       </c>
       <c r="B78" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92521</v>
+        <v>92534</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93449</v>
+        <v>93462</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93449</v>
+        <v>93462</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93449</v>
+        <v>93462</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93449</v>
+        <v>93462</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81470</v>
+        <v>81472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91497</v>
+        <v>91499</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>137017516</v>
       </c>
       <c r="B56" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>137017522</v>
       </c>
       <c r="B78" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92534</v>
+        <v>92536</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93462</v>
+        <v>93463</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93462</v>
+        <v>93463</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93462</v>
+        <v>93463</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93462</v>
+        <v>93463</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -6716,11 +6716,7 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hällskär, Vb</t>
@@ -9405,11 +9401,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90876</v>
+        <v>90879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92536</v>
+        <v>92539</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93463</v>
+        <v>93466</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93463</v>
+        <v>93466</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93463</v>
+        <v>93466</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93463</v>
+        <v>93466</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90879</v>
+        <v>90889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91502</v>
+        <v>91512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>137017516</v>
       </c>
       <c r="B56" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>137017522</v>
       </c>
       <c r="B78" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92539</v>
+        <v>92549</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93466</v>
+        <v>93476</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93466</v>
+        <v>93476</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93466</v>
+        <v>93476</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93466</v>
+        <v>93476</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93476</v>
+        <v>93477</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93476</v>
+        <v>93477</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93476</v>
+        <v>93477</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93476</v>
+        <v>93477</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81482</v>
+        <v>81485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91513</v>
+        <v>91516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>137017516</v>
       </c>
       <c r="B56" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>137017522</v>
       </c>
       <c r="B78" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92550</v>
+        <v>92553</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93477</v>
+        <v>93482</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93477</v>
+        <v>93482</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93477</v>
+        <v>93482</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93477</v>
+        <v>93482</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92553</v>
+        <v>92555</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93482</v>
+        <v>93484</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93482</v>
+        <v>93484</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93482</v>
+        <v>93484</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93482</v>
+        <v>93484</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90893</v>
+        <v>90898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90756</v>
+        <v>90761</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91518</v>
+        <v>91523</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>137017516</v>
       </c>
       <c r="B56" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>137017522</v>
       </c>
       <c r="B78" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92555</v>
+        <v>92560</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93484</v>
+        <v>93490</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93484</v>
+        <v>93490</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93484</v>
+        <v>93490</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93484</v>
+        <v>93490</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -5243,6 +5243,9 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hällskär, Vb</t>
@@ -5303,6 +5306,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -10213,7 +10217,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90898</v>
+        <v>90909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91523</v>
+        <v>91535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92560</v>
+        <v>92572</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90909</v>
+        <v>90910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92572</v>
+        <v>92573</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90910</v>
+        <v>90913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92573</v>
+        <v>92576</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81504</v>
+        <v>81505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90776</v>
+        <v>90777</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91539</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92576</v>
+        <v>92577</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93506</v>
+        <v>93507</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93506</v>
+        <v>93507</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93506</v>
+        <v>93507</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93506</v>
+        <v>93507</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137017510</v>
       </c>
       <c r="B3" t="n">
-        <v>81505</v>
+        <v>81508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>137016784</v>
       </c>
       <c r="B7" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137016787</v>
       </c>
       <c r="B8" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137016794</v>
       </c>
       <c r="B12" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137017509</v>
       </c>
       <c r="B13" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137016790</v>
       </c>
       <c r="B15" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137017513</v>
       </c>
       <c r="B16" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137017505</v>
       </c>
       <c r="B18" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137017518</v>
       </c>
       <c r="B19" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137016795</v>
       </c>
       <c r="B20" t="n">
-        <v>90777</v>
+        <v>90780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>137017514</v>
       </c>
       <c r="B24" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>137017521</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>137016788</v>
       </c>
       <c r="B34" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137016796</v>
       </c>
       <c r="B35" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137016800</v>
       </c>
       <c r="B36" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>137017494</v>
       </c>
       <c r="B37" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>137017520</v>
       </c>
       <c r="B38" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>137016789</v>
       </c>
       <c r="B41" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137016797</v>
       </c>
       <c r="B42" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>137017498</v>
       </c>
       <c r="B43" t="n">
-        <v>90967</v>
+        <v>90971</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>137017523</v>
       </c>
       <c r="B44" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>137016791</v>
       </c>
       <c r="B45" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>137016785</v>
       </c>
       <c r="B51" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>137016798</v>
       </c>
       <c r="B52" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>137017496</v>
       </c>
       <c r="B53" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>137017516</v>
       </c>
       <c r="B56" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>137017522</v>
       </c>
       <c r="B78" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>137017512</v>
       </c>
       <c r="B85" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>137016786</v>
       </c>
       <c r="B86" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>137017506</v>
       </c>
       <c r="B88" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>137017497</v>
       </c>
       <c r="B89" t="n">
-        <v>93507</v>
+        <v>93510</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137017500</v>
       </c>
       <c r="B90" t="n">
-        <v>93507</v>
+        <v>93510</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>137017502</v>
       </c>
       <c r="B91" t="n">
-        <v>93507</v>
+        <v>93510</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>137017524</v>
       </c>
       <c r="B92" t="n">
-        <v>93507</v>
+        <v>93510</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
